--- a/SLIDE_MANIFEST.xlsx
+++ b/SLIDE_MANIFEST.xlsx
@@ -1,40 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - DCTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - RegE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - Attrition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - Mailer" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - Value" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARS - Insights" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - General" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Merchant" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - MCC Code" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Competition" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Financial Svc" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Campaign" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Branch" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - TXN Type" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Product" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Attrition" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Balance" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Interchange" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - RegE Overdraft" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Payroll" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Relationship" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Segment Evol" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Retention" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Engagement" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TXN - Executive" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preamble" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout Reference" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Key" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ARS - Overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ARS - DCTR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ARS - RegE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ARS - Attrition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ARS - Mailer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ARS - Value" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ARS - Insights" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TXN - General" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TXN - Merchant" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TXN - MCC Code" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TXN - Competition" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TXN - Financial Svc" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TXN - Campaign" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TXN - Branch" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TXN - TXN Type" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TXN - Product" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TXN - Attrition" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TXN - Balance" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TXN - Interchange" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TXN - RegE Overdraft" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TXN - Payroll" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TXN - Relationship" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="TXN - Segment Evol" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TXN - Retention" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TXN - Engagement" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TXN - Executive" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Preamble" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Layout Reference" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Support Deck" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +73,15 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +92,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000274C"/>
         <bgColor rgb="0000274C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3D59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7E7F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,6 +133,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +500,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Keep on MAIN deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Move to Support Deck (appendix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Drop entirely</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Not yet decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Group ID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;SECTION&gt;-MAIN-&lt;n&gt;</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Slides with the same Group ID compose onto a single slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (left)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Goes on the LEFT of a 2-up slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (right)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Goes on the RIGHT of a 2-up slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Single-chart slide, wide canvas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SECTION_ALT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Section divider</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -552,25 +762,25 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>TXN-MERCH-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Account Composition</t>
+          <t>Merchant Data Aggregation</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Horizontal bar (status breakdown)</t>
+          <t>Data prep</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>CONTENT</t>
+          <t>CUSTOM</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -588,17 +798,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A1b</t>
+          <t>TXN-MERCH-02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Product Code Distribution</t>
+          <t>Merchant KPIs</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Horizontal bar (product mix)</t>
+          <t>KPI cards</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -624,17 +834,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>TXN-MERCH-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Eligibility Funnel</t>
+          <t>Top 20 Merchants Bar</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>KPI cards + donut</t>
+          <t>Horizontal bar</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -653,13 +863,409 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Donut</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Donut chart</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Concentration</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Pareto chart</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Trend</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Growth</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Volatility</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Merchant Lifecycle</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Biz vs Personal</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>By Age</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>By Engagement</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>New Entrants</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>TXN-MERCH-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Action Summary</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Bullet list</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>BULLETS</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1277,7 +1883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2543,7 +3149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3305,7 +3911,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4931,7 +5537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5369,7 +5975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6023,7 +6629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6461,7 +7067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6965,444 +7571,6 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Slide #</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Slide ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Title Pattern</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Chart Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Layout #</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Layout Name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Slide Type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Keep? (Y/N)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Your Layout Choice</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-01</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Balance Data</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Data prep</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Balance KPIs</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>KPI cards</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-03</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Balance Distribution</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Histogram</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-04</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Balance Bands Bar</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-05</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Balance vs Activity</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Scatter</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-06</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Deposit Flight Risk</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-07</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Balance by Demographics</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-08</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>PFI Scoring</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>KPI + distribution</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-09</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Balance vs Competitor</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>TWO_CONTENT</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>TXN-BAL-10</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Action Summary</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Bullet list</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>BULLETS</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7488,12 +7656,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-01</t>
+          <t>TXN-BAL-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Interchange Data</t>
+          <t>Balance Data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7524,12 +7692,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-02</t>
+          <t>TXN-BAL-02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Interchange KPIs</t>
+          <t>Balance KPIs</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -7560,17 +7728,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-03</t>
+          <t>TXN-BAL-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PIN/SIG Trend</t>
+          <t>Balance Distribution</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Histogram</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -7596,17 +7764,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-04</t>
+          <t>TXN-BAL-04</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PIN/SIG Ratio</t>
+          <t>Balance Bands Bar</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Stacked bar</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -7632,25 +7800,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-05</t>
+          <t>TXN-BAL-05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Revenue Waterfall</t>
+          <t>Balance vs Activity</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>Scatter</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>CONTENT</t>
+          <t>CUSTOM</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7668,12 +7836,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-06</t>
+          <t>TXN-BAL-06</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PIN Heavy Accounts</t>
+          <t>Deposit Flight Risk</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7704,12 +7872,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-07</t>
+          <t>TXN-BAL-07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>By Demographics</t>
+          <t>Balance by Demographics</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -7740,17 +7908,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-08</t>
+          <t>TXN-BAL-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>By Merchant</t>
+          <t>PFI Scoring</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Horizontal bar</t>
+          <t>KPI + distribution</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -7776,12 +7944,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-09</t>
+          <t>TXN-BAL-09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>By Product</t>
+          <t>Balance vs Competitor</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7790,11 +7958,11 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>CONTENT</t>
+          <t>TWO_CONTENT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7812,7 +7980,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TXN-IC-10</t>
+          <t>TXN-BAL-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7853,7 +8021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7926,25 +8094,25 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>DCTR-2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Historical Debit Card Take Rate</t>
+          <t>Account Composition</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Horizontal bar (status breakdown)</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>CONTENT</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -7962,25 +8130,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>DCTR-3</t>
+          <t>A1b</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>L12M Snapshot</t>
+          <t>Product Code Distribution</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Horizontal bar (product mix)</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>CONTENT</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -7998,25 +8166,25 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DCTR-4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Open vs Eligible Comparison</t>
+          <t>Eligibility Funnel</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>KPI cards + donut</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>CONTENT</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8027,1014 +8195,6 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-5</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Personal vs Business Split</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Stacked bar</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-6</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Monthly Trend</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Branch Comparison</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Horizontal bar</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-8</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Age Distribution</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-9</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Product Code Analysis</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-10</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Cohort Analysis</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-11</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>New Account Activation</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-12</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Dormant Reactivation</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-13</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>PIN vs Signature Split</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Stacked bar</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-14</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Spend per Active Card</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-15</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Swipes per Active Card</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>DCTR-16</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Revenue per Card</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>A7.4</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Trajectory: Segments</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>A7.5</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Eligible Trend</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>A7.6a</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Trajectory: Recent Trend</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>A7.6b</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Segment Detail</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>A7.7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Funnel: Historical</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Funnel</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>A7.8</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Funnel: TTM</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Funnel</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>A7.9</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Eligible vs Non-Eligible</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>A7.10a</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Eligible vs Non-Eligible Overlay</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>A7.10b</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Overlay Detail</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>A7.10c</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Overlay KPI</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>KPI cards</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>screenshot_kpi</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>A7.11</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Opportunity: Age Analysis</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>A7.12</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>DCTR Opportunity: Age Detail</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>A7.13</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Product Breakdown</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>A7.14</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Tenure Analysis</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>A7.15</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>[Appendix] Branch Detail</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Horizontal bar</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>A11.1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Value of a Debit Card</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Waterfall</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9120,12 +8280,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-01</t>
+          <t>TXN-IC-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RegE Data</t>
+          <t>Interchange Data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9156,12 +8316,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-02</t>
+          <t>TXN-IC-02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RegE KPIs</t>
+          <t>Interchange KPIs</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9192,12 +8352,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-03</t>
+          <t>TXN-IC-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Opt-In Trend</t>
+          <t>PIN/SIG Trend</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9228,12 +8388,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-04</t>
+          <t>TXN-IC-04</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Opt-In Migration</t>
+          <t>PIN/SIG Ratio</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -9264,17 +8424,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-05</t>
+          <t>TXN-IC-05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>OD Limit Distribution</t>
+          <t>Revenue Waterfall</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Histogram</t>
+          <t>Waterfall</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -9300,17 +8460,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-06</t>
+          <t>TXN-IC-06</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>OD Limit Trend</t>
+          <t>PIN Heavy Accounts</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -9336,7 +8496,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-07</t>
+          <t>TXN-IC-07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -9372,17 +8532,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-08</t>
+          <t>TXN-IC-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Revenue Exposure</t>
+          <t>By Merchant</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>Horizontal bar</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -9408,25 +8568,25 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-09</t>
+          <t>TXN-IC-09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RegE vs Balance</t>
+          <t>By Product</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Scatter</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>CONTENT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9444,7 +8604,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TXN-REGE-10</t>
+          <t>TXN-IC-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -9558,12 +8718,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-01</t>
+          <t>TXN-REGE-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Payroll Data</t>
+          <t>RegE Data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9594,12 +8754,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-02</t>
+          <t>TXN-REGE-02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Payroll KPIs</t>
+          <t>RegE KPIs</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9630,17 +8790,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-03</t>
+          <t>TXN-REGE-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Payroll Distribution</t>
+          <t>Opt-In Trend</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -9666,17 +8826,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-04</t>
+          <t>TXN-REGE-04</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Payroll Value</t>
+          <t>Opt-In Migration</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Stacked bar</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -9702,17 +8862,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-05</t>
+          <t>TXN-REGE-05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>By Demographics</t>
+          <t>OD Limit Distribution</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Histogram</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -9738,17 +8898,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-06</t>
+          <t>TXN-REGE-06</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Payroll Processors</t>
+          <t>OD Limit Trend</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Horizontal bar</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -9774,17 +8934,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-07</t>
+          <t>TXN-REGE-07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Payroll Retention</t>
+          <t>By Demographics</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -9810,17 +8970,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-08</t>
+          <t>TXN-REGE-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PFI Composite Score</t>
+          <t>Revenue Exposure</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>KPI + chart</t>
+          <t>Waterfall</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -9846,25 +9006,25 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-09</t>
+          <t>TXN-REGE-09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PFI vs Competitor</t>
+          <t>RegE vs Balance</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Scatter</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>TWO_CONTENT</t>
+          <t>CUSTOM</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9882,7 +9042,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TXN-PAY-10</t>
+          <t>TXN-REGE-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -9996,12 +9156,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-01</t>
+          <t>TXN-PAY-01</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Relationship Data</t>
+          <t>Payroll Data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -10032,12 +9192,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-02</t>
+          <t>TXN-PAY-02</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Relationship KPIs</t>
+          <t>Payroll KPIs</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -10068,12 +9228,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-03</t>
+          <t>TXN-PAY-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Product Count Bar</t>
+          <t>Payroll Distribution</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -10104,12 +9264,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-04</t>
+          <t>TXN-PAY-04</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Single Product Risk</t>
+          <t>Payroll Value</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -10140,25 +9300,25 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-05</t>
+          <t>TXN-PAY-05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cross-Sell Matrix</t>
+          <t>By Demographics</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Heatmap</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>CONTENT</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10176,17 +9336,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-06</t>
+          <t>TXN-PAY-06</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Relationship Value</t>
+          <t>Payroll Processors</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Horizontal bar</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -10212,17 +9372,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-07</t>
+          <t>TXN-PAY-07</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Leakage Opportunity</t>
+          <t>Payroll Retention</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -10248,17 +9408,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-08</t>
+          <t>TXN-PAY-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>By Demographics</t>
+          <t>PFI Composite Score</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>KPI + chart</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -10284,25 +9444,25 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-09</t>
+          <t>TXN-PAY-09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Next Best Product</t>
+          <t>PFI vs Competitor</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>CUSTOM</t>
+          <t>TWO_CONTENT</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10320,7 +9480,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TXN-REL-10</t>
+          <t>TXN-PAY-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10356,6 +9516,444 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Slide #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Slide ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title Pattern</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chart Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Layout #</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Slide Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Relationship Data</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Data prep</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Relationship KPIs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>KPI cards</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Product Count Bar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Single Product Risk</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Sell Matrix</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Heatmap</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Relationship Value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Leakage Opportunity</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Waterfall</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>By Demographics</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CONTENT</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Next Best Product</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TXN-REL-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Action Summary</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Bullet list</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>BULLETS</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10721,7 +10319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11051,7 +10649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11345,7 +10943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11603,7 +11201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12149,7 +11747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12557,7 +12155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12618,7 +12216,12 @@
           <t>Your Layout Choice</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Group ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -12630,17 +12233,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>A8.1</t>
+          <t>DCTR-2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>[Appendix] Overall Status</t>
+          <t>Historical Debit Card Take Rate</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Stacked bar + KPI</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
@@ -12656,9 +12259,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -12666,17 +12277,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A8.2</t>
+          <t>DCTR-3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>[Appendix] Historical Year/Decade</t>
+          <t>L12M Snapshot</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -12692,9 +12303,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -12702,17 +12321,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>A8.3</t>
+          <t>DCTR-4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>L12M Monthly Opt-In Trend</t>
+          <t>Open vs Eligible Comparison</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
@@ -12728,9 +12347,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -12738,17 +12365,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>A8.4a</t>
+          <t>DCTR-5</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Branch Comparison (Horizontal)</t>
+          <t>Personal vs Business Split</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Horizontal bar</t>
+          <t>Stacked bar</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -12764,9 +12391,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -12774,17 +12409,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A8.4b</t>
+          <t>DCTR-6</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Branch Comparison (Combo)</t>
+          <t>Monthly Trend</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Combo chart</t>
+          <t>Line chart</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -12800,9 +12435,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -12810,17 +12453,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A8.4c</t>
+          <t>DCTR-7</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>[Appendix] Branch Scatter</t>
+          <t>Branch Comparison</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Scatter</t>
+          <t>Horizontal bar</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -12836,9 +12479,26 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (right)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DCTR-MAIN-1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 1 RIGHT. Enhance: vertical combo -- branches on X, column = eligible opens per branch, 2 lines = historical take rate + L12M take rate.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -12846,17 +12506,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>A8.5</t>
+          <t>DCTR-8</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Opportunity: Account Age</t>
+          <t>Age Distribution</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -12872,9 +12532,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -12882,17 +12550,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A8.6</t>
+          <t>DCTR-9</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Opportunity: Holder Age</t>
+          <t>Product Code Analysis</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Grouped bar</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -12908,9 +12576,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -12918,17 +12594,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A8.7</t>
+          <t>DCTR-10</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>[Appendix] Product Code Breakdown</t>
+          <t>Cohort Analysis</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bar chart</t>
+          <t>Grouped bar</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -12944,9 +12620,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -12954,17 +12638,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A8.10</t>
+          <t>DCTR-11</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Funnel: All-Time</t>
+          <t>New Account Activation</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Funnel</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -12980,9 +12664,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -12990,17 +12682,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A8.11</t>
+          <t>DCTR-12</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Funnel: TTM</t>
+          <t>Dormant Reactivation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Funnel</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -13016,9 +12708,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -13026,17 +12726,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A8.12</t>
+          <t>DCTR-13</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>[Appendix] 24-Month Trend</t>
+          <t>PIN vs Signature Split</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Line chart</t>
+          <t>Stacked bar</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -13052,9 +12752,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -13062,17 +12770,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A8.13</t>
+          <t>DCTR-14</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Branch x Month Pivot</t>
+          <t>Spend per Active Card</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Heatmap</t>
+          <t>Bar chart</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -13088,9 +12796,17 @@
           <t>screenshot</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -13098,35 +12814,2138 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>A11.2</t>
+          <t>DCTR-15</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Value of Reg E Opt-In</t>
+          <t>Swipes per Active Card</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>DCTR-16</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Revenue per Card</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>A7.4</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Trajectory: Segments</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>A7.5</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Eligible Trend</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>A7.6a</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Trajectory: Recent Trend</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (left)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DCTR-MAIN-1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 1 LEFT. Enhance: add monthly volume bars to existing rate line (bar+line combo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>A7.6b</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Segment Detail</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>A7.7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Funnel: Historical</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Funnel</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (left)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DCTR-MAIN-2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 2 LEFT. Historical funnel as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>A7.8</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Funnel: TTM</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Funnel</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (right)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DCTR-MAIN-2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 2 RIGHT. L12M funnel as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>A7.9</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Eligible vs Non-Eligible</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>A7.10a</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Eligible vs Non-Eligible Overlay</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>A7.10b</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Overlay Detail</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>A7.10c</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Overlay KPI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>KPI cards</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>screenshot_kpi</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>A7.11</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Opportunity: Age Analysis</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>A7.12</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>DCTR Opportunity: Age Detail</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>A7.13</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Product Breakdown</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>A7.14</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Tenure Analysis</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>A7.15</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Branch Detail</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal bar</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>A11.1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Value of a Debit Card</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Waterfall</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="E32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DCTR-MAIN-3</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 3. Single hero slide - Value of Debit Card waterfall.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Slide #</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Slide ID</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Title Pattern</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Chart Type</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Original Layout</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DCTR-2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Historical Debit Card Take Rate</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DCTR-3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L12M Snapshot</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DCTR-4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open vs Eligible Comparison</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DCTR-5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Personal vs Business Split</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stacked bar</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DCTR-6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Monthly Trend</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DCTR-8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Age Distribution</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DCTR-9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Product Code Analysis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DCTR-10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cohort Analysis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DCTR-11</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>New Account Activation</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DCTR-12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dormant Reactivation</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DCTR-13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PIN vs Signature Split</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Stacked bar</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DCTR-14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Spend per Active Card</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DCTR-15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Swipes per Active Card</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DCTR-16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Revenue per Card</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A7.4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DCTR Trajectory: Segments</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A7.5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[Appendix] Eligible Trend</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A7.6b</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[Appendix] Segment Detail</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A7.9</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[Appendix] Eligible vs Non-Eligible</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A7.10a</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Eligible vs Non-Eligible Overlay</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>24</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A7.10b</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[Appendix] Overlay Detail</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A7.10c</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[Appendix] Overlay KPI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KPI cards</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A7.11</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DCTR Opportunity: Age Analysis</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>27</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A7.12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DCTR Opportunity: Age Detail</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>28</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A7.13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[Appendix] Product Breakdown</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>29</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A7.14</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[Appendix] Tenure Analysis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ARS - DCTR</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>A7.15</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[Appendix] Branch Detail</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Horizontal bar</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>A8.1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[Appendix] Overall Status</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stacked bar + KPI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>A8.2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[Appendix] Historical Year/Decade</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>A8.4b</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Branch Comparison (Combo)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Combo chart</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A8.4c</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[Appendix] Branch Scatter</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Scatter</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A8.5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Opportunity: Account Age</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A8.6</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Opportunity: Holder Age</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A8.7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[Appendix] Product Code Breakdown</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A8.12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[Appendix] 24-Month Trend</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ARS - RegE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A8.13</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Branch x Month Pivot</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Heatmap</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13134,6 +14953,750 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Slide #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Slide ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title Pattern</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chart Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Layout #</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Layout Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Slide Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Keep? (Y/N)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Your Layout Choice</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Group ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>A8.1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Overall Status</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Stacked bar + KPI</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A8.2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Historical Year/Decade</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A8.3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>L12M Monthly Opt-In Trend</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (left)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>REGE-MAIN-1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 1 LEFT. Enhance: add monthly volume bars (eligible opens) alongside existing opt-in rate line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A8.4a</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Branch Comparison (Horizontal)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal bar</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (right)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>REGE-MAIN-1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 1 RIGHT. Enhance: vertical combo -- branches on X, column = eligible opens per branch, 2 lines = historical opt-in rate + L12M opt-in rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A8.4b</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Branch Comparison (Combo)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Combo chart</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A8.4c</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Branch Scatter</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Scatter</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>A8.5</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity: Account Age</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>A8.6</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity: Holder Age</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Grouped bar</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>A8.7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] Product Code Breakdown</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>A8.10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Funnel: All-Time</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Funnel</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (left)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>REGE-MAIN-2</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 2 LEFT. All-time funnel as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>A8.11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Funnel: TTM</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Funnel</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>TWO_CONTENT (right)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>REGE-MAIN-2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 2 RIGHT. TTM funnel as-is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>A8.12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>[Appendix] 24-Month Trend</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>A8.13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Branch x Month Pivot</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Heatmap</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Support deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>A11.2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Value of Reg E Opt-In</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Waterfall</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>screenshot</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>CUSTOM</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>REGE-MAIN-3</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MAIN slide 3. Single hero slide - Value of Reg E Opt-In waterfall.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13679,7 +16242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14477,7 +17040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14627,7 +17190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15281,7 +17844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16401,586 +18964,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Slide #</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Slide ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Title Pattern</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Chart Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Layout #</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Layout Name</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Slide Type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Keep? (Y/N)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Your Layout Choice</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-01</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Data Aggregation</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Data prep</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOM</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Merchant KPIs</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>KPI cards</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-03</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Top 20 Merchants Bar</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Horizontal bar</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-04</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Donut</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Donut chart</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-05</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Concentration</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Pareto chart</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-06</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Trend</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-07</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Growth</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-08</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Volatility</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Line chart</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-09</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Merchant Lifecycle</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-10</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Biz vs Personal</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>TWO_CONTENT</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-11</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>By Age</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-12</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>By Engagement</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Grouped bar</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-13</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>New Entrants</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Bar chart</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>CONTENT</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>TXN-MERCH-14</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Action Summary</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Bullet list</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>BULLETS</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>screenshot</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>